--- a/data/trans_bre/P05B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P05B_R-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,94</t>
+          <t>-3,84; 1,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,71</t>
+          <t>-2,14; 3,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,27</t>
+          <t>-4,53; 3,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,13; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,55</t>
+          <t>-100,0; 195,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,95; 377,31</t>
+          <t>-63,67; 334,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,83; 102,44</t>
+          <t>-62,07; 108,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-6,62%</t>
+          <t>-9,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,43</t>
+          <t>-0,76; 4,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,77</t>
+          <t>-3,59; 1,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,8</t>
+          <t>-0,19; 4,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,8</t>
+          <t>-1,4; 0,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 189,98</t>
+          <t>-20,31; 173,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 54,46</t>
+          <t>-55,43; 53,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 306,74</t>
+          <t>-14,02; 302,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,57; 462,96</t>
+          <t>-87,79; 461,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-20,74%</t>
+          <t>-20,34%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,02</t>
+          <t>-0,58; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,28</t>
+          <t>-1,53; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,87</t>
+          <t>-3,82; 1,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 259,6</t>
+          <t>-12,97; 285,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,37; 93,93</t>
+          <t>-66,35; 91,87</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,41%</t>
+          <t>-4,95%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,35</t>
+          <t>-2,3; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,55</t>
+          <t>-1,32; 2,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,65</t>
+          <t>-0,04; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,03</t>
+          <t>-2,72; 1,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,66; 186,63</t>
+          <t>-56,49; 157,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 525,22</t>
+          <t>-62,16; 400,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 785,47</t>
+          <t>-21,35; 913,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 61,42</t>
+          <t>-65,66; 126,02</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-66,33%</t>
+          <t>-57,34%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,59</t>
+          <t>-2,93; 7,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,69</t>
+          <t>-2,35; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,86</t>
+          <t>0,4; 3,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,17</t>
+          <t>-1,58; 0,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 156,03</t>
+          <t>-33,82; 145,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,16; 449,48</t>
+          <t>-74,93; 428,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,03</t>
+          <t>-1,06; 3,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,82</t>
+          <t>-1,78; 0,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,48</t>
+          <t>-0,63; 1,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,32</t>
+          <t>-1,62; 1,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>-72,69; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>135,51%</t>
+          <t>175,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,83</t>
+          <t>2,19; 6,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,24</t>
+          <t>-0,84; 1,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,84</t>
+          <t>-0,93; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,12</t>
+          <t>0,22; 2,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,56; 467,65</t>
+          <t>70,65; 503,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,39; 527,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 292,97</t>
+          <t>-55,37; 295,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 795,5</t>
+          <t>7,01; 842,34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,01</t>
+          <t>-0,75; 2,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,49</t>
+          <t>-1,51; 0,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,44</t>
+          <t>-0,09; 1,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,12</t>
+          <t>-0,58; 0,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 174,81</t>
+          <t>-24,63; 151,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,46; 132,46</t>
+          <t>-87,12; 165,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,32; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 1395,49</t>
+          <t>-73,86; 454,4</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,67</t>
+          <t>0,81; 2,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,62</t>
+          <t>-0,66; 0,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,46</t>
+          <t>0,13; 1,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,65</t>
+          <t>-0,35; 0,64</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,44; 108,36</t>
+          <t>23,25; 101,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 47,56</t>
+          <t>-33,18; 47,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,97; 136,62</t>
+          <t>6,54; 127,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-27,96; 85,03</t>
+          <t>-26,5; 73,67</t>
         </is>
       </c>
     </row>
